--- a/data/gravel/Bulls Grinder 2025.xlsx
+++ b/data/gravel/Bulls Grinder 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3270A00C-CA6F-C145-8681-E9A37CB47FED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9A7B96D-476F-2141-A76E-BCE0DF91E0D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3400" yWindow="520" windowWidth="25400" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7640" yWindow="700" windowWidth="25400" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="108">
   <si>
     <t>brand</t>
   </si>
@@ -350,16 +350,13 @@
     <t>aluminum</t>
   </si>
   <si>
-    <t>what's up with these top tube length differences?</t>
-  </si>
-  <si>
     <t>https://velomotion.net/2025/05/bulls-grinder-4/</t>
   </si>
   <si>
-    <t>carbe machete</t>
-  </si>
-  <si>
     <t>Grinder</t>
+  </si>
+  <si>
+    <t>* there is an error in Grinder 4 chart for top tube</t>
   </si>
 </sst>
 </file>
@@ -744,7 +741,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
@@ -783,9 +780,7 @@
       <c r="B7" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>107</v>
-      </c>
+      <c r="H7" s="1"/>
     </row>
     <row r="8" spans="1:16" ht="24" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -804,18 +799,10 @@
         <v>7</v>
       </c>
       <c r="G8" s="5"/>
-      <c r="I8" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2" t="s">
         <v>70</v>
@@ -832,36 +819,26 @@
         <v>89</v>
       </c>
       <c r="C9" s="6">
-        <v>450</v>
+        <v>546</v>
       </c>
       <c r="D9" s="6">
-        <v>470</v>
+        <v>569</v>
       </c>
       <c r="E9" s="6">
-        <v>510</v>
+        <v>587</v>
       </c>
       <c r="F9" s="6">
-        <v>550</v>
-      </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="I9" s="6">
-        <v>546</v>
-      </c>
-      <c r="J9" s="6">
-        <v>570</v>
-      </c>
-      <c r="K9" s="6">
-        <v>587</v>
-      </c>
-      <c r="L9" s="6">
         <v>610</v>
       </c>
-      <c r="M9" s="1" t="s">
-        <v>105</v>
-      </c>
+      <c r="G9" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="1"/>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
@@ -886,21 +863,11 @@
         <v>424</v>
       </c>
       <c r="G10" s="5"/>
-      <c r="H10" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="I10" s="6">
-        <v>381</v>
-      </c>
-      <c r="J10" s="6">
-        <v>398</v>
-      </c>
-      <c r="K10" s="6">
-        <v>407</v>
-      </c>
-      <c r="L10" s="6">
-        <v>424</v>
-      </c>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
@@ -925,21 +892,11 @@
         <v>649</v>
       </c>
       <c r="G11" s="5"/>
-      <c r="H11" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="I11" s="6">
-        <v>575</v>
-      </c>
-      <c r="J11" s="6">
-        <v>599</v>
-      </c>
-      <c r="K11" s="6">
-        <v>626</v>
-      </c>
-      <c r="L11" s="6">
-        <v>649</v>
-      </c>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
@@ -964,21 +921,11 @@
         <v>550</v>
       </c>
       <c r="G12" s="5"/>
-      <c r="H12" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="I12" s="6">
-        <v>450</v>
-      </c>
-      <c r="J12" s="6">
-        <v>470</v>
-      </c>
-      <c r="K12" s="6">
-        <v>510</v>
-      </c>
-      <c r="L12" s="6">
-        <v>550</v>
-      </c>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
@@ -1003,21 +950,11 @@
         <v>74</v>
       </c>
       <c r="G13" s="5"/>
-      <c r="H13" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="I13" s="6">
-        <v>74</v>
-      </c>
-      <c r="J13" s="6">
-        <v>74</v>
-      </c>
-      <c r="K13" s="6">
-        <v>74</v>
-      </c>
-      <c r="L13" s="6">
-        <v>74</v>
-      </c>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
     </row>
@@ -1041,21 +978,11 @@
         <v>435</v>
       </c>
       <c r="G14" s="5"/>
-      <c r="H14" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="I14" s="6">
-        <v>419</v>
-      </c>
-      <c r="J14" s="6">
-        <v>419</v>
-      </c>
-      <c r="K14" s="6">
-        <v>419</v>
-      </c>
-      <c r="L14" s="6">
-        <v>419</v>
-      </c>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
     </row>
@@ -1079,21 +1006,11 @@
         <v>1100</v>
       </c>
       <c r="G15" s="5"/>
-      <c r="H15" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="I15" s="6">
-        <v>1016</v>
-      </c>
-      <c r="J15" s="6">
-        <v>1041</v>
-      </c>
-      <c r="K15" s="6">
-        <v>1060</v>
-      </c>
-      <c r="L15" s="6">
-        <v>1084</v>
-      </c>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
@@ -1118,21 +1035,11 @@
         <v>70</v>
       </c>
       <c r="G16" s="5"/>
-      <c r="H16" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="I16" s="6">
-        <v>70</v>
-      </c>
-      <c r="J16" s="6">
-        <v>70</v>
-      </c>
-      <c r="K16" s="6">
-        <v>70</v>
-      </c>
-      <c r="L16" s="6">
-        <v>70</v>
-      </c>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
     </row>
@@ -1156,21 +1063,11 @@
         <v>71</v>
       </c>
       <c r="G17" s="5"/>
-      <c r="H17" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="I17" s="6">
-        <v>71</v>
-      </c>
-      <c r="J17" s="6">
-        <v>71</v>
-      </c>
-      <c r="K17" s="6">
-        <v>71</v>
-      </c>
-      <c r="L17" s="6">
-        <v>71</v>
-      </c>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
@@ -1195,21 +1092,11 @@
         <v>213</v>
       </c>
       <c r="G18" s="5"/>
-      <c r="H18" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="I18" s="6">
-        <v>135</v>
-      </c>
-      <c r="J18" s="6">
-        <v>160</v>
-      </c>
-      <c r="K18" s="6">
-        <v>189</v>
-      </c>
-      <c r="L18" s="6">
-        <v>213</v>
-      </c>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
@@ -1389,7 +1276,7 @@
         <v>85</v>
       </c>
       <c r="C38" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
@@ -1405,7 +1292,7 @@
         <v>50</v>
       </c>
       <c r="C40" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
